--- a/outputs/Block2_2026_Fold_Summary_v12.xlsx
+++ b/outputs/Block2_2026_Fold_Summary_v12.xlsx
@@ -453,28 +453,28 @@
         <v>10</v>
       </c>
       <c r="B2">
-        <v>4.784274033149172</v>
+        <v>7.05637923250565</v>
       </c>
       <c r="C2">
-        <v>4.784274033149169</v>
+        <v>7.056379232505655</v>
       </c>
       <c r="D2">
-        <v>-3.552713678800501E-15</v>
+        <v>5.329070518200751E-15</v>
       </c>
       <c r="E2">
-        <v>0.008509136249528836</v>
+        <v>0.01255022013825051</v>
       </c>
       <c r="F2">
-        <v>0.01522160566700327</v>
+        <v>0.02245051628937196</v>
       </c>
       <c r="G2">
-        <v>4.770475138121549</v>
+        <v>7.036027088036134</v>
       </c>
       <c r="H2">
-        <v>4.790187845303867</v>
+        <v>7.065101580135458</v>
       </c>
       <c r="I2">
-        <v>0.01971270718231821</v>
+        <v>0.02907449209932444</v>
       </c>
       <c r="J2" t="s">
         <v>13</v>
@@ -485,28 +485,28 @@
         <v>11</v>
       </c>
       <c r="B3">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="C3">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="D3">
         <v>-1</v>
       </c>
       <c r="E3">
-        <v>6.284902544988268</v>
+        <v>9.273618495495704</v>
       </c>
       <c r="F3">
-        <v>11.24277545804416</v>
+        <v>16.58915308266218</v>
       </c>
       <c r="G3">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="H3">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="I3">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="J3" t="s">
         <v>13</v>
@@ -517,28 +517,28 @@
         <v>12</v>
       </c>
       <c r="B4">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C4">
-        <v>48.4</v>
+        <v>48.6</v>
       </c>
       <c r="D4">
-        <v>0.3999999999999986</v>
+        <v>-1.399999999999999</v>
       </c>
       <c r="E4">
-        <v>1.51657508881031</v>
+        <v>1.816590212458495</v>
       </c>
       <c r="F4">
-        <v>2.712931993250108</v>
+        <v>3.249615361854384</v>
       </c>
       <c r="G4">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H4">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J4" t="s">
         <v>13</v>
